--- a/engagement_survey_forms/025_manager_feedback_request--engagement_survey_forms.xlsx
+++ b/engagement_survey_forms/025_manager_feedback_request--engagement_survey_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'1',_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': '1', 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'2',_'label':_'team_members'}</t>
+          <t>team_members</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': '2', 'label': 'Team Members'}</t>
+          <t>Team Members</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'3',_'label':_'department'}</t>
+          <t>department</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': '3', 'label': 'Department'}</t>
+          <t>Department</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'1',_'label':_'communication'}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': '1', 'label': 'Communication'}</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'2',_'label':_'leadership'}</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': '2', 'label': 'Leadership'}</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'3',_'label':_'problem_solving'}</t>
+          <t>problem_solving</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': '3', 'label': 'Problem Solving'}</t>
+          <t>Problem Solving</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'4',_'label':_'adaptability'}</t>
+          <t>adaptability</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': '4', 'label': 'Adaptability'}</t>
+          <t>Adaptability</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'5',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': '5', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'1',_'label':_'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': '1', 'label': 'Positive'}</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'2',_'label':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': '2', 'label': 'Negative'}</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'3',_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': '3', 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
